--- a/meteran_air.xlsx
+++ b/meteran_air.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>Tanggal</t>
   </si>
@@ -31,16 +31,31 @@
     <t>17-04-2026</t>
   </si>
   <si>
+    <t>28-04-2026</t>
+  </si>
+  <si>
+    <t>12-05-2026</t>
+  </si>
+  <si>
     <t>91. CO2 BOTTLED</t>
   </si>
   <si>
     <t>1. DEEPWELL 1 AQUADUCT SIPA</t>
   </si>
   <si>
+    <t>4. STATIC WATER LEVEL (JTL)</t>
+  </si>
+  <si>
+    <t>42. PASTEURIZER</t>
+  </si>
+  <si>
     <t>Error OCR</t>
   </si>
   <si>
     <t>57803.9</t>
+  </si>
+  <si>
+    <t>589301.13</t>
   </si>
 </sst>
 </file>
@@ -398,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -417,10 +432,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -428,10 +443,54 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/meteran_air.xlsx
+++ b/meteran_air.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Tanggal</t>
   </si>
@@ -25,34 +25,10 @@
     <t>Angka Meteran</t>
   </si>
   <si>
-    <t>13-04-2026</t>
-  </si>
-  <si>
-    <t>17-04-2026</t>
-  </si>
-  <si>
-    <t>28-04-2026</t>
-  </si>
-  <si>
-    <t>12-05-2026</t>
-  </si>
-  <si>
-    <t>91. CO2 BOTTLED</t>
+    <t>15-05-2026</t>
   </si>
   <si>
     <t>1. DEEPWELL 1 AQUADUCT SIPA</t>
-  </si>
-  <si>
-    <t>4. STATIC WATER LEVEL (JTL)</t>
-  </si>
-  <si>
-    <t>42. PASTEURIZER</t>
-  </si>
-  <si>
-    <t>Error OCR</t>
-  </si>
-  <si>
-    <t>57803.9</t>
   </si>
   <si>
     <t>589301.13</t>
@@ -413,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -432,65 +408,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
